--- a/output/Data and Chart Outputs/turkey_generation_mix_dashboard_daily.xlsx
+++ b/output/Data and Chart Outputs/turkey_generation_mix_dashboard_daily.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -145,13 +145,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -161,6 +161,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <areaChart>
@@ -174,10 +175,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -202,10 +203,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -230,10 +231,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -258,10 +259,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EDA100"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -286,10 +287,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="E87BA4"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -314,10 +315,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="008300"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -342,10 +343,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4A3AA7"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -370,10 +371,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="9A9A9A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -398,11 +399,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
@@ -419,8 +432,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -430,13 +443,14 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -444,12 +458,13 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -458,7 +473,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>10</col>
@@ -473,9 +488,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/output/Data and Chart Outputs/turkey_generation_mix_dashboard_daily.xlsx
+++ b/output/Data and Chart Outputs/turkey_generation_mix_dashboard_daily.xlsx
@@ -156,7 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Turkey generation mix (to Sep/26)</a:t>
+              <a:t>Turkey generation mix (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -185,12 +185,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2</f>
+              <f>'Chart'!$B$2:$B$3</f>
             </numRef>
           </val>
         </ser>
@@ -213,12 +213,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2</f>
+              <f>'Chart'!$C$2:$C$3</f>
             </numRef>
           </val>
         </ser>
@@ -241,12 +241,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2</f>
+              <f>'Chart'!$D$2:$D$3</f>
             </numRef>
           </val>
         </ser>
@@ -269,12 +269,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2</f>
+              <f>'Chart'!$E$2:$E$3</f>
             </numRef>
           </val>
         </ser>
@@ -297,12 +297,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2</f>
+              <f>'Chart'!$F$2:$F$3</f>
             </numRef>
           </val>
         </ser>
@@ -325,12 +325,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2</f>
+              <f>'Chart'!$G$2:$G$3</f>
             </numRef>
           </val>
         </ser>
@@ -353,12 +353,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2</f>
+              <f>'Chart'!$H$2:$H$3</f>
             </numRef>
           </val>
         </ser>
@@ -381,12 +381,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2</f>
+              <f>'Chart'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2</f>
+              <f>'Chart'!$I$2:$I$3</f>
             </numRef>
           </val>
         </ser>
@@ -931,7 +931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1011,6 +1011,35 @@
       </c>
       <c r="I2" t="n">
         <v>88.36652173913043</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B3" t="n">
+        <v>13200.72</v>
+      </c>
+      <c r="C3" t="n">
+        <v>10525.78086956522</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4257.407826086956</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3437.620869565219</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1199.085217391304</v>
+      </c>
+      <c r="G3" t="n">
+        <v>966.0604347826087</v>
+      </c>
+      <c r="H3" t="n">
+        <v>884.191304347826</v>
+      </c>
+      <c r="I3" t="n">
+        <v>109.2473913043478</v>
       </c>
     </row>
   </sheetData>
@@ -1025,7 +1054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1168,47 @@
         <v>23</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B3" t="n">
+        <v>884.191304347826</v>
+      </c>
+      <c r="C3" t="n">
+        <v>966.0604347826087</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1199.085217391304</v>
+      </c>
+      <c r="E3" t="n">
+        <v>86.24739130434784</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3437.620869565219</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4257.407826086956</v>
+      </c>
+      <c r="H3" t="n">
+        <v>13200.72</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10525.78086956522</v>
+      </c>
+      <c r="J3" t="n">
+        <v>108.0678260869565</v>
+      </c>
+      <c r="K3" t="n">
+        <v>34665.18173913043</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.5144218134025926</v>
+      </c>
+      <c r="M3" t="n">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/turkey_generation_mix_dashboard_daily.xlsx
+++ b/output/Data and Chart Outputs/turkey_generation_mix_dashboard_daily.xlsx
@@ -185,12 +185,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$3</f>
+              <f>'Chart'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$3</f>
+              <f>'Chart'!$B$2:$B$4</f>
             </numRef>
           </val>
         </ser>
@@ -213,12 +213,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$3</f>
+              <f>'Chart'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$3</f>
+              <f>'Chart'!$C$2:$C$4</f>
             </numRef>
           </val>
         </ser>
@@ -241,12 +241,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$3</f>
+              <f>'Chart'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$3</f>
+              <f>'Chart'!$D$2:$D$4</f>
             </numRef>
           </val>
         </ser>
@@ -269,12 +269,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$3</f>
+              <f>'Chart'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$3</f>
+              <f>'Chart'!$E$2:$E$4</f>
             </numRef>
           </val>
         </ser>
@@ -297,12 +297,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$3</f>
+              <f>'Chart'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$3</f>
+              <f>'Chart'!$F$2:$F$4</f>
             </numRef>
           </val>
         </ser>
@@ -325,12 +325,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$3</f>
+              <f>'Chart'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$3</f>
+              <f>'Chart'!$G$2:$G$4</f>
             </numRef>
           </val>
         </ser>
@@ -353,12 +353,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$3</f>
+              <f>'Chart'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$3</f>
+              <f>'Chart'!$H$2:$H$4</f>
             </numRef>
           </val>
         </ser>
@@ -381,12 +381,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$3</f>
+              <f>'Chart'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$3</f>
+              <f>'Chart'!$I$2:$I$4</f>
             </numRef>
           </val>
         </ser>
@@ -931,7 +931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1040,6 +1040,35 @@
       </c>
       <c r="I3" t="n">
         <v>109.2473913043478</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B4" t="n">
+        <v>13589.15590909091</v>
+      </c>
+      <c r="C4" t="n">
+        <v>10519.53363636364</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2022.361363636364</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4338.223181818182</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1173.492272727273</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1277.467272727273</v>
+      </c>
+      <c r="H4" t="n">
+        <v>831.2363636363636</v>
+      </c>
+      <c r="I4" t="n">
+        <v>103.345</v>
       </c>
     </row>
   </sheetData>
@@ -1054,7 +1083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1209,6 +1238,47 @@
         <v>23</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B4" t="n">
+        <v>831.2363636363636</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1277.467272727273</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1173.492272727273</v>
+      </c>
+      <c r="E4" t="n">
+        <v>81.34499999999998</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4338.223181818182</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2022.361363636364</v>
+      </c>
+      <c r="H4" t="n">
+        <v>13589.15590909091</v>
+      </c>
+      <c r="I4" t="n">
+        <v>10519.53363636364</v>
+      </c>
+      <c r="J4" t="n">
+        <v>104.6045454545454</v>
+      </c>
+      <c r="K4" t="n">
+        <v>33937.41954545455</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.4662726607100077</v>
+      </c>
+      <c r="M4" t="n">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/turkey_generation_mix_dashboard_daily.xlsx
+++ b/output/Data and Chart Outputs/turkey_generation_mix_dashboard_daily.xlsx
@@ -1047,28 +1047,28 @@
         <v>46302</v>
       </c>
       <c r="B4" t="n">
-        <v>13589.15590909091</v>
+        <v>13930.33652173913</v>
       </c>
       <c r="C4" t="n">
-        <v>10519.53363636364</v>
+        <v>10682.54304347826</v>
       </c>
       <c r="D4" t="n">
-        <v>2022.361363636364</v>
+        <v>2007.883913043478</v>
       </c>
       <c r="E4" t="n">
-        <v>4338.223181818182</v>
+        <v>4553.062173913043</v>
       </c>
       <c r="F4" t="n">
-        <v>1173.492272727273</v>
+        <v>1203.572173913044</v>
       </c>
       <c r="G4" t="n">
-        <v>1277.467272727273</v>
+        <v>1222.35</v>
       </c>
       <c r="H4" t="n">
-        <v>831.2363636363636</v>
+        <v>870.8639130434785</v>
       </c>
       <c r="I4" t="n">
-        <v>103.345</v>
+        <v>111.9773913043478</v>
       </c>
     </row>
   </sheetData>
@@ -1243,40 +1243,40 @@
         <v>46302</v>
       </c>
       <c r="B4" t="n">
-        <v>831.2363636363636</v>
+        <v>870.8639130434785</v>
       </c>
       <c r="C4" t="n">
-        <v>1277.467272727273</v>
+        <v>1222.35</v>
       </c>
       <c r="D4" t="n">
-        <v>1173.492272727273</v>
+        <v>1203.572173913044</v>
       </c>
       <c r="E4" t="n">
-        <v>81.34499999999998</v>
+        <v>88.9773913043478</v>
       </c>
       <c r="F4" t="n">
-        <v>4338.223181818182</v>
+        <v>4553.062173913043</v>
       </c>
       <c r="G4" t="n">
-        <v>2022.361363636364</v>
+        <v>2007.883913043478</v>
       </c>
       <c r="H4" t="n">
-        <v>13589.15590909091</v>
+        <v>13930.33652173913</v>
       </c>
       <c r="I4" t="n">
-        <v>10519.53363636364</v>
+        <v>10682.54304347826</v>
       </c>
       <c r="J4" t="n">
-        <v>104.6045454545454</v>
+        <v>109.5265217391304</v>
       </c>
       <c r="K4" t="n">
-        <v>33937.41954545455</v>
+        <v>34669.11565217391</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4662726607100077</v>
+        <v>0.4611370305453923</v>
       </c>
       <c r="M4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/turkey_generation_mix_dashboard_daily.xlsx
+++ b/output/Data and Chart Outputs/turkey_generation_mix_dashboard_daily.xlsx
@@ -156,6 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Turkey generation mix (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -176,7 +177,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -185,12 +186,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$4</f>
+              <f>'Chart'!$J$2:$J$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$4</f>
+              <f>'Chart'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -204,7 +205,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EB6834"/>
+              <a:srgbClr val="2A78D6"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -213,12 +214,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$4</f>
+              <f>'Chart'!$J$2:$J$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$4</f>
+              <f>'Chart'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -241,12 +242,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$4</f>
+              <f>'Chart'!$J$2:$J$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$4</f>
+              <f>'Chart'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -269,12 +270,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$4</f>
+              <f>'Chart'!$J$2:$J$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$4</f>
+              <f>'Chart'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -288,7 +289,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="A0522D"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -297,12 +298,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$4</f>
+              <f>'Chart'!$J$2:$J$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$4</f>
+              <f>'Chart'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -316,7 +317,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="EDA100"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -325,12 +326,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$4</f>
+              <f>'Chart'!$J$2:$J$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$4</f>
+              <f>'Chart'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -344,7 +345,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
+              <a:srgbClr val="8A9A2B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -353,12 +354,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$4</f>
+              <f>'Chart'!$J$2:$J$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$4</f>
+              <f>'Chart'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -381,12 +382,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$4</f>
+              <f>'Chart'!$J$2:$J$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$4</f>
+              <f>'Chart'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -931,7 +932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -983,6 +984,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Axis label</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
@@ -1012,6 +1018,11 @@
       <c r="I2" t="n">
         <v>88.36652173913043</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Sep/26</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -1041,6 +1052,11 @@
       <c r="I3" t="n">
         <v>109.2473913043478</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Oct/26</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -1069,6 +1085,35 @@
       </c>
       <c r="I4" t="n">
         <v>111.9773913043478</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B5" t="n">
+        <v>13455.955</v>
+      </c>
+      <c r="C5" t="n">
+        <v>10397.61181818182</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1106.979090909091</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5399.756818181818</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1176.295</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1326.133636363636</v>
+      </c>
+      <c r="H5" t="n">
+        <v>870.635909090909</v>
+      </c>
+      <c r="I5" t="n">
+        <v>111.5286363636364</v>
       </c>
     </row>
   </sheetData>
@@ -1083,7 +1128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1279,6 +1324,47 @@
         <v>23</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B5" t="n">
+        <v>870.635909090909</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1326.133636363636</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1176.295</v>
+      </c>
+      <c r="E5" t="n">
+        <v>89.52863636363635</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5399.756818181818</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1106.979090909091</v>
+      </c>
+      <c r="H5" t="n">
+        <v>13455.955</v>
+      </c>
+      <c r="I5" t="n">
+        <v>10397.61181818182</v>
+      </c>
+      <c r="J5" t="n">
+        <v>98.72272727272728</v>
+      </c>
+      <c r="K5" t="n">
+        <v>33921.61863636363</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.4385891962890225</v>
+      </c>
+      <c r="M5" t="n">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/turkey_generation_mix_dashboard_daily.xlsx
+++ b/output/Data and Chart Outputs/turkey_generation_mix_dashboard_daily.xlsx
@@ -1092,28 +1092,28 @@
         <v>46303</v>
       </c>
       <c r="B5" t="n">
-        <v>13455.955</v>
+        <v>14084.24086956521</v>
       </c>
       <c r="C5" t="n">
-        <v>10397.61181818182</v>
+        <v>10536.91173913044</v>
       </c>
       <c r="D5" t="n">
-        <v>1106.979090909091</v>
+        <v>1128.955652173913</v>
       </c>
       <c r="E5" t="n">
-        <v>5399.756818181818</v>
+        <v>5514.582173913043</v>
       </c>
       <c r="F5" t="n">
-        <v>1176.295</v>
+        <v>1207.023913043478</v>
       </c>
       <c r="G5" t="n">
-        <v>1326.133636363636</v>
+        <v>1273.707826086956</v>
       </c>
       <c r="H5" t="n">
-        <v>870.635909090909</v>
+        <v>907.1395652173915</v>
       </c>
       <c r="I5" t="n">
-        <v>111.5286363636364</v>
+        <v>114.5647826086957</v>
       </c>
     </row>
   </sheetData>
@@ -1329,40 +1329,40 @@
         <v>46303</v>
       </c>
       <c r="B5" t="n">
-        <v>870.635909090909</v>
+        <v>907.1395652173915</v>
       </c>
       <c r="C5" t="n">
-        <v>1326.133636363636</v>
+        <v>1273.707826086956</v>
       </c>
       <c r="D5" t="n">
-        <v>1176.295</v>
+        <v>1207.023913043478</v>
       </c>
       <c r="E5" t="n">
-        <v>89.52863636363635</v>
+        <v>91.56478260869567</v>
       </c>
       <c r="F5" t="n">
-        <v>5399.756818181818</v>
+        <v>5514.582173913043</v>
       </c>
       <c r="G5" t="n">
-        <v>1106.979090909091</v>
+        <v>1128.955652173913</v>
       </c>
       <c r="H5" t="n">
-        <v>13455.955</v>
+        <v>14084.24086956521</v>
       </c>
       <c r="I5" t="n">
-        <v>10397.61181818182</v>
+        <v>10536.91173913044</v>
       </c>
       <c r="J5" t="n">
-        <v>98.72272727272728</v>
+        <v>100.4004347826087</v>
       </c>
       <c r="K5" t="n">
-        <v>33921.61863636363</v>
+        <v>34844.52695652174</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4385891962890225</v>
+        <v>0.4320259165646275</v>
       </c>
       <c r="M5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/turkey_generation_mix_dashboard_daily.xlsx
+++ b/output/Data and Chart Outputs/turkey_generation_mix_dashboard_daily.xlsx
@@ -186,12 +186,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$5</f>
+              <f>'Chart'!$J$2:$J$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$5</f>
+              <f>'Chart'!$B$2:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -214,12 +214,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$5</f>
+              <f>'Chart'!$J$2:$J$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$5</f>
+              <f>'Chart'!$C$2:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -242,12 +242,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$5</f>
+              <f>'Chart'!$J$2:$J$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$5</f>
+              <f>'Chart'!$D$2:$D$6</f>
             </numRef>
           </val>
         </ser>
@@ -261,7 +261,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EDA100"/>
+              <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -270,12 +270,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$5</f>
+              <f>'Chart'!$J$2:$J$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$5</f>
+              <f>'Chart'!$E$2:$E$6</f>
             </numRef>
           </val>
         </ser>
@@ -298,12 +298,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$5</f>
+              <f>'Chart'!$J$2:$J$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$5</f>
+              <f>'Chart'!$F$2:$F$6</f>
             </numRef>
           </val>
         </ser>
@@ -326,12 +326,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$5</f>
+              <f>'Chart'!$J$2:$J$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$5</f>
+              <f>'Chart'!$G$2:$G$6</f>
             </numRef>
           </val>
         </ser>
@@ -354,12 +354,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$5</f>
+              <f>'Chart'!$J$2:$J$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$5</f>
+              <f>'Chart'!$H$2:$H$6</f>
             </numRef>
           </val>
         </ser>
@@ -382,12 +382,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$5</f>
+              <f>'Chart'!$J$2:$J$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$5</f>
+              <f>'Chart'!$I$2:$I$6</f>
             </numRef>
           </val>
         </ser>
@@ -932,7 +932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -956,12 +956,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>gas</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>wind</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>gas</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -1001,10 +1001,10 @@
         <v>10624.66956521739</v>
       </c>
       <c r="D2" t="n">
+        <v>2260.416956521739</v>
+      </c>
+      <c r="E2" t="n">
         <v>8939.307826086957</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2260.416956521739</v>
       </c>
       <c r="F2" t="n">
         <v>1144.379565217391</v>
@@ -1035,10 +1035,10 @@
         <v>10525.78086956522</v>
       </c>
       <c r="D3" t="n">
+        <v>3437.620869565219</v>
+      </c>
+      <c r="E3" t="n">
         <v>4257.407826086956</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3437.620869565219</v>
       </c>
       <c r="F3" t="n">
         <v>1199.085217391304</v>
@@ -1069,10 +1069,10 @@
         <v>10682.54304347826</v>
       </c>
       <c r="D4" t="n">
+        <v>4553.062173913043</v>
+      </c>
+      <c r="E4" t="n">
         <v>2007.883913043478</v>
-      </c>
-      <c r="E4" t="n">
-        <v>4553.062173913043</v>
       </c>
       <c r="F4" t="n">
         <v>1203.572173913044</v>
@@ -1098,10 +1098,10 @@
         <v>10536.91173913044</v>
       </c>
       <c r="D5" t="n">
+        <v>5514.582173913043</v>
+      </c>
+      <c r="E5" t="n">
         <v>1128.955652173913</v>
-      </c>
-      <c r="E5" t="n">
-        <v>5514.582173913043</v>
       </c>
       <c r="F5" t="n">
         <v>1207.023913043478</v>
@@ -1114,6 +1114,35 @@
       </c>
       <c r="I5" t="n">
         <v>114.5647826086957</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B6" t="n">
+        <v>12966.69727272727</v>
+      </c>
+      <c r="C6" t="n">
+        <v>10778.54772727273</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4329.511363636364</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1704.248636363636</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1181.419545454545</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1339.551818181818</v>
+      </c>
+      <c r="H6" t="n">
+        <v>866.9286363636364</v>
+      </c>
+      <c r="I6" t="n">
+        <v>108.9740909090909</v>
       </c>
     </row>
   </sheetData>
@@ -1128,7 +1157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1365,6 +1394,47 @@
         <v>23</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B6" t="n">
+        <v>866.9286363636364</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1339.551818181818</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1181.419545454545</v>
+      </c>
+      <c r="E6" t="n">
+        <v>86.9740909090909</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4329.511363636364</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1704.248636363636</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12966.69727272727</v>
+      </c>
+      <c r="I6" t="n">
+        <v>10778.54772727273</v>
+      </c>
+      <c r="J6" t="n">
+        <v>106.0868181818182</v>
+      </c>
+      <c r="K6" t="n">
+        <v>33359.96590909091</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.4757407848342989</v>
+      </c>
+      <c r="M6" t="n">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/turkey_generation_mix_dashboard_daily.xlsx
+++ b/output/Data and Chart Outputs/turkey_generation_mix_dashboard_daily.xlsx
@@ -1121,28 +1121,28 @@
         <v>46304</v>
       </c>
       <c r="B6" t="n">
-        <v>12966.69727272727</v>
+        <v>13423.46391304348</v>
       </c>
       <c r="C6" t="n">
-        <v>10778.54772727273</v>
+        <v>10881.23608695652</v>
       </c>
       <c r="D6" t="n">
-        <v>4329.511363636364</v>
+        <v>4533.611304347826</v>
       </c>
       <c r="E6" t="n">
-        <v>1704.248636363636</v>
+        <v>1677.721304347826</v>
       </c>
       <c r="F6" t="n">
-        <v>1181.419545454545</v>
+        <v>1188.747391304348</v>
       </c>
       <c r="G6" t="n">
-        <v>1339.551818181818</v>
+        <v>1281.619130434782</v>
       </c>
       <c r="H6" t="n">
-        <v>866.9286363636364</v>
+        <v>896.6608695652175</v>
       </c>
       <c r="I6" t="n">
-        <v>108.9740909090909</v>
+        <v>106.3526086956522</v>
       </c>
     </row>
   </sheetData>
@@ -1399,40 +1399,40 @@
         <v>46304</v>
       </c>
       <c r="B6" t="n">
-        <v>866.9286363636364</v>
+        <v>896.6608695652175</v>
       </c>
       <c r="C6" t="n">
-        <v>1339.551818181818</v>
+        <v>1281.619130434782</v>
       </c>
       <c r="D6" t="n">
-        <v>1181.419545454545</v>
+        <v>1188.747391304348</v>
       </c>
       <c r="E6" t="n">
-        <v>86.9740909090909</v>
+        <v>83.35260869565217</v>
       </c>
       <c r="F6" t="n">
-        <v>4329.511363636364</v>
+        <v>4533.611304347826</v>
       </c>
       <c r="G6" t="n">
-        <v>1704.248636363636</v>
+        <v>1677.721304347826</v>
       </c>
       <c r="H6" t="n">
-        <v>12966.69727272727</v>
+        <v>13423.46391304348</v>
       </c>
       <c r="I6" t="n">
-        <v>10778.54772727273</v>
+        <v>10881.23608695652</v>
       </c>
       <c r="J6" t="n">
-        <v>106.0868181818182</v>
+        <v>108.7495652173913</v>
       </c>
       <c r="K6" t="n">
-        <v>33359.96590909091</v>
+        <v>34075.16217391304</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4757407848342989</v>
+        <v>0.4673781067079167</v>
       </c>
       <c r="M6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/turkey_generation_mix_dashboard_daily.xlsx
+++ b/output/Data and Chart Outputs/turkey_generation_mix_dashboard_daily.xlsx
@@ -186,12 +186,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$6</f>
+              <f>'Chart'!$J$2:$J$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$6</f>
+              <f>'Chart'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -214,12 +214,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$6</f>
+              <f>'Chart'!$J$2:$J$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$6</f>
+              <f>'Chart'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -242,12 +242,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$6</f>
+              <f>'Chart'!$J$2:$J$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$6</f>
+              <f>'Chart'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -270,12 +270,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$6</f>
+              <f>'Chart'!$J$2:$J$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$6</f>
+              <f>'Chart'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -289,7 +289,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="A0522D"/>
+              <a:srgbClr val="EDA100"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -298,12 +298,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$6</f>
+              <f>'Chart'!$J$2:$J$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$6</f>
+              <f>'Chart'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -317,7 +317,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EDA100"/>
+              <a:srgbClr val="A0522D"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -326,12 +326,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$6</f>
+              <f>'Chart'!$J$2:$J$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$6</f>
+              <f>'Chart'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -354,12 +354,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$6</f>
+              <f>'Chart'!$J$2:$J$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$6</f>
+              <f>'Chart'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -382,12 +382,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$6</f>
+              <f>'Chart'!$J$2:$J$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$6</f>
+              <f>'Chart'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -932,7 +932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -966,12 +966,12 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>geothermal</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>solar</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -1007,10 +1007,10 @@
         <v>8939.307826086957</v>
       </c>
       <c r="F2" t="n">
+        <v>1014.253043478261</v>
+      </c>
+      <c r="G2" t="n">
         <v>1144.379565217391</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1014.253043478261</v>
       </c>
       <c r="H2" t="n">
         <v>845.441304347826</v>
@@ -1041,10 +1041,10 @@
         <v>4257.407826086956</v>
       </c>
       <c r="F3" t="n">
+        <v>966.0604347826087</v>
+      </c>
+      <c r="G3" t="n">
         <v>1199.085217391304</v>
-      </c>
-      <c r="G3" t="n">
-        <v>966.0604347826087</v>
       </c>
       <c r="H3" t="n">
         <v>884.191304347826</v>
@@ -1075,10 +1075,10 @@
         <v>2007.883913043478</v>
       </c>
       <c r="F4" t="n">
+        <v>1222.35</v>
+      </c>
+      <c r="G4" t="n">
         <v>1203.572173913044</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1222.35</v>
       </c>
       <c r="H4" t="n">
         <v>870.8639130434785</v>
@@ -1104,10 +1104,10 @@
         <v>1128.955652173913</v>
       </c>
       <c r="F5" t="n">
+        <v>1273.707826086956</v>
+      </c>
+      <c r="G5" t="n">
         <v>1207.023913043478</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1273.707826086956</v>
       </c>
       <c r="H5" t="n">
         <v>907.1395652173915</v>
@@ -1133,16 +1133,45 @@
         <v>1677.721304347826</v>
       </c>
       <c r="F6" t="n">
+        <v>1281.619130434782</v>
+      </c>
+      <c r="G6" t="n">
         <v>1188.747391304348</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1281.619130434782</v>
       </c>
       <c r="H6" t="n">
         <v>896.6608695652175</v>
       </c>
       <c r="I6" t="n">
         <v>106.3526086956522</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B7" t="n">
+        <v>13189.48</v>
+      </c>
+      <c r="C7" t="n">
+        <v>9089.283636363636</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4899.940909090909</v>
+      </c>
+      <c r="E7" t="n">
+        <v>689.2968181818183</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1367.291818181818</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1148.251363636364</v>
+      </c>
+      <c r="H7" t="n">
+        <v>867.8440909090909</v>
+      </c>
+      <c r="I7" t="n">
+        <v>105.9422727272727</v>
       </c>
     </row>
   </sheetData>
@@ -1157,7 +1186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1435,6 +1464,47 @@
         <v>23</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B7" t="n">
+        <v>867.8440909090909</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1367.291818181818</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1148.251363636364</v>
+      </c>
+      <c r="E7" t="n">
+        <v>83.94227272727272</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4899.940909090909</v>
+      </c>
+      <c r="G7" t="n">
+        <v>689.2968181818183</v>
+      </c>
+      <c r="H7" t="n">
+        <v>13189.48</v>
+      </c>
+      <c r="I7" t="n">
+        <v>9089.283636363636</v>
+      </c>
+      <c r="J7" t="n">
+        <v>112.8818181818182</v>
+      </c>
+      <c r="K7" t="n">
+        <v>31448.21272727273</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.418528322783136</v>
+      </c>
+      <c r="M7" t="n">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/turkey_generation_mix_dashboard_daily.xlsx
+++ b/output/Data and Chart Outputs/turkey_generation_mix_dashboard_daily.xlsx
@@ -289,7 +289,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EDA100"/>
+              <a:srgbClr val="A0522D"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -317,7 +317,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="A0522D"/>
+              <a:srgbClr val="EDA100"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -966,12 +966,12 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>geothermal</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>solar</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>geothermal</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -1007,10 +1007,10 @@
         <v>8939.307826086957</v>
       </c>
       <c r="F2" t="n">
+        <v>1144.379565217391</v>
+      </c>
+      <c r="G2" t="n">
         <v>1014.253043478261</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1144.379565217391</v>
       </c>
       <c r="H2" t="n">
         <v>845.441304347826</v>
@@ -1041,10 +1041,10 @@
         <v>4257.407826086956</v>
       </c>
       <c r="F3" t="n">
+        <v>1199.085217391304</v>
+      </c>
+      <c r="G3" t="n">
         <v>966.0604347826087</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1199.085217391304</v>
       </c>
       <c r="H3" t="n">
         <v>884.191304347826</v>
@@ -1075,10 +1075,10 @@
         <v>2007.883913043478</v>
       </c>
       <c r="F4" t="n">
+        <v>1203.572173913044</v>
+      </c>
+      <c r="G4" t="n">
         <v>1222.35</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1203.572173913044</v>
       </c>
       <c r="H4" t="n">
         <v>870.8639130434785</v>
@@ -1104,10 +1104,10 @@
         <v>1128.955652173913</v>
       </c>
       <c r="F5" t="n">
+        <v>1207.023913043478</v>
+      </c>
+      <c r="G5" t="n">
         <v>1273.707826086956</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1207.023913043478</v>
       </c>
       <c r="H5" t="n">
         <v>907.1395652173915</v>
@@ -1133,10 +1133,10 @@
         <v>1677.721304347826</v>
       </c>
       <c r="F6" t="n">
+        <v>1188.747391304348</v>
+      </c>
+      <c r="G6" t="n">
         <v>1281.619130434782</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1188.747391304348</v>
       </c>
       <c r="H6" t="n">
         <v>896.6608695652175</v>
@@ -1150,28 +1150,28 @@
         <v>46305</v>
       </c>
       <c r="B7" t="n">
-        <v>13189.48</v>
+        <v>13387.14434782609</v>
       </c>
       <c r="C7" t="n">
-        <v>9089.283636363636</v>
+        <v>9301.552608695652</v>
       </c>
       <c r="D7" t="n">
-        <v>4899.940909090909</v>
+        <v>5037.752608695652</v>
       </c>
       <c r="E7" t="n">
-        <v>689.2968181818183</v>
+        <v>706.1852173913045</v>
       </c>
       <c r="F7" t="n">
-        <v>1367.291818181818</v>
+        <v>1162.914782608696</v>
       </c>
       <c r="G7" t="n">
-        <v>1148.251363636364</v>
+        <v>1309.732608695652</v>
       </c>
       <c r="H7" t="n">
-        <v>867.8440909090909</v>
+        <v>898.3826086956522</v>
       </c>
       <c r="I7" t="n">
-        <v>105.9422727272727</v>
+        <v>106.8360869565217</v>
       </c>
     </row>
   </sheetData>
@@ -1469,40 +1469,40 @@
         <v>46305</v>
       </c>
       <c r="B7" t="n">
-        <v>867.8440909090909</v>
+        <v>898.3826086956522</v>
       </c>
       <c r="C7" t="n">
-        <v>1367.291818181818</v>
+        <v>1309.732608695652</v>
       </c>
       <c r="D7" t="n">
-        <v>1148.251363636364</v>
+        <v>1162.914782608696</v>
       </c>
       <c r="E7" t="n">
-        <v>83.94227272727272</v>
+        <v>83.83608695652174</v>
       </c>
       <c r="F7" t="n">
-        <v>4899.940909090909</v>
+        <v>5037.752608695652</v>
       </c>
       <c r="G7" t="n">
-        <v>689.2968181818183</v>
+        <v>706.1852173913045</v>
       </c>
       <c r="H7" t="n">
-        <v>13189.48</v>
+        <v>13387.14434782609</v>
       </c>
       <c r="I7" t="n">
-        <v>9089.283636363636</v>
+        <v>9301.552608695652</v>
       </c>
       <c r="J7" t="n">
-        <v>112.8818181818182</v>
+        <v>114.9030434782609</v>
       </c>
       <c r="K7" t="n">
-        <v>31448.21272727273</v>
+        <v>32002.40391304348</v>
       </c>
       <c r="L7" t="n">
-        <v>0.418528322783136</v>
+        <v>0.418055089312652</v>
       </c>
       <c r="M7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/turkey_generation_mix_dashboard_daily.xlsx
+++ b/output/Data and Chart Outputs/turkey_generation_mix_dashboard_daily.xlsx
@@ -186,12 +186,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$7</f>
+              <f>'Chart'!$J$2:$J$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$7</f>
+              <f>'Chart'!$B$2:$B$8</f>
             </numRef>
           </val>
         </ser>
@@ -214,12 +214,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$7</f>
+              <f>'Chart'!$J$2:$J$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$7</f>
+              <f>'Chart'!$C$2:$C$8</f>
             </numRef>
           </val>
         </ser>
@@ -242,12 +242,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$7</f>
+              <f>'Chart'!$J$2:$J$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$7</f>
+              <f>'Chart'!$D$2:$D$8</f>
             </numRef>
           </val>
         </ser>
@@ -270,12 +270,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$7</f>
+              <f>'Chart'!$J$2:$J$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$7</f>
+              <f>'Chart'!$E$2:$E$8</f>
             </numRef>
           </val>
         </ser>
@@ -298,12 +298,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$7</f>
+              <f>'Chart'!$J$2:$J$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$7</f>
+              <f>'Chart'!$F$2:$F$8</f>
             </numRef>
           </val>
         </ser>
@@ -326,12 +326,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$7</f>
+              <f>'Chart'!$J$2:$J$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$7</f>
+              <f>'Chart'!$G$2:$G$8</f>
             </numRef>
           </val>
         </ser>
@@ -354,12 +354,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$7</f>
+              <f>'Chart'!$J$2:$J$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$7</f>
+              <f>'Chart'!$H$2:$H$8</f>
             </numRef>
           </val>
         </ser>
@@ -382,12 +382,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$7</f>
+              <f>'Chart'!$J$2:$J$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$7</f>
+              <f>'Chart'!$I$2:$I$8</f>
             </numRef>
           </val>
         </ser>
@@ -932,7 +932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1172,6 +1172,35 @@
       </c>
       <c r="I7" t="n">
         <v>106.8360869565217</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B8" t="n">
+        <v>12134.79136363636</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7875.047272727273</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2766.688636363636</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2129.277727272727</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1137.042727272727</v>
+      </c>
+      <c r="G8" t="n">
+        <v>999.9590909090911</v>
+      </c>
+      <c r="H8" t="n">
+        <v>840.5154545454548</v>
+      </c>
+      <c r="I8" t="n">
+        <v>100.2568181818182</v>
       </c>
     </row>
   </sheetData>
@@ -1186,7 +1215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1505,6 +1534,47 @@
         <v>23</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B8" t="n">
+        <v>840.5154545454548</v>
+      </c>
+      <c r="C8" t="n">
+        <v>999.9590909090911</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1137.042727272727</v>
+      </c>
+      <c r="E8" t="n">
+        <v>78.25681818181819</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2766.688636363636</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2129.277727272727</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12134.79136363636</v>
+      </c>
+      <c r="I8" t="n">
+        <v>7875.047272727273</v>
+      </c>
+      <c r="J8" t="n">
+        <v>112.3654545454545</v>
+      </c>
+      <c r="K8" t="n">
+        <v>28073.94454545455</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.4624160403148322</v>
+      </c>
+      <c r="M8" t="n">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/turkey_generation_mix_dashboard_daily.xlsx
+++ b/output/Data and Chart Outputs/turkey_generation_mix_dashboard_daily.xlsx
@@ -21,8 +21,8 @@
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="167" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,12 +62,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -991,7 +992,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="5" t="n">
         <v>46295</v>
       </c>
       <c r="B2" t="n">
@@ -1025,7 +1026,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="5" t="n">
         <v>46301</v>
       </c>
       <c r="B3" t="n">
@@ -1059,7 +1060,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="5" t="n">
         <v>46302</v>
       </c>
       <c r="B4" t="n">
@@ -1088,7 +1089,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="5" t="n">
         <v>46303</v>
       </c>
       <c r="B5" t="n">
@@ -1117,7 +1118,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="5" t="n">
         <v>46304</v>
       </c>
       <c r="B6" t="n">
@@ -1146,7 +1147,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="5" t="n">
         <v>46305</v>
       </c>
       <c r="B7" t="n">
@@ -1175,7 +1176,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="5" t="n">
         <v>46306</v>
       </c>
       <c r="B8" t="n">

--- a/output/Data and Chart Outputs/turkey_generation_mix_dashboard_daily.xlsx
+++ b/output/Data and Chart Outputs/turkey_generation_mix_dashboard_daily.xlsx
@@ -21,8 +21,8 @@
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,13 +62,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -992,7 +991,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="4" t="n">
         <v>46295</v>
       </c>
       <c r="B2" t="n">
@@ -1026,7 +1025,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="4" t="n">
         <v>46301</v>
       </c>
       <c r="B3" t="n">
@@ -1060,7 +1059,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="4" t="n">
         <v>46302</v>
       </c>
       <c r="B4" t="n">
@@ -1089,7 +1088,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="4" t="n">
         <v>46303</v>
       </c>
       <c r="B5" t="n">
@@ -1118,7 +1117,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="4" t="n">
         <v>46304</v>
       </c>
       <c r="B6" t="n">
@@ -1147,7 +1146,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="4" t="n">
         <v>46305</v>
       </c>
       <c r="B7" t="n">
@@ -1176,7 +1175,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="4" t="n">
         <v>46306</v>
       </c>
       <c r="B8" t="n">
